--- a/output/topology_excel/4697.xlsx
+++ b/output/topology_excel/4697.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,7 +465,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B20" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B21" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B27" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="B29" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="B30" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B32" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>1</v>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="B35" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,10 +1202,10 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="F35" t="n">
-        <v>158</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
@@ -1213,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="B36" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,18 +1224,18 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>455</v>
+        <v>194</v>
       </c>
       <c r="F36" t="n">
-        <v>286</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B37" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>326</v>
+        <v>156</v>
       </c>
       <c r="F37" t="n">
         <v>16</v>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B38" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,18 +1268,18 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>212</v>
+        <v>342</v>
       </c>
       <c r="F38" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B39" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,18 +1290,18 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>110</v>
+        <v>277</v>
       </c>
       <c r="F39" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B40" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,18 +1312,18 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="F40" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>309</v>
+        <v>94</v>
       </c>
       <c r="F41" t="n">
         <v>16</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B42" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,18 +1356,18 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F42" t="n">
-        <v>56</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,18 +1378,18 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>323</v>
+        <v>142</v>
       </c>
       <c r="F43" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B44" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,18 +1400,18 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>232</v>
+        <v>439</v>
       </c>
       <c r="F44" t="n">
-        <v>218</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B45" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,18 +1422,18 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>128</v>
+        <v>309</v>
       </c>
       <c r="F45" t="n">
-        <v>127</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,18 +1444,18 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>325</v>
+        <v>218</v>
       </c>
       <c r="F46" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B47" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,18 +1466,18 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>114</v>
+        <v>323</v>
       </c>
       <c r="F47" t="n">
-        <v>94</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>99</v>
+        <v>158</v>
       </c>
       <c r="F48" t="n">
         <v>16</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B49" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>30</v>
+        <v>325</v>
       </c>
       <c r="F49" t="n">
         <v>16</v>
@@ -1518,10 +1518,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B50" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,18 +1532,18 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>247</v>
+        <v>323</v>
       </c>
       <c r="F50" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B51" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,18 +1554,18 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>144</v>
+        <v>429</v>
       </c>
       <c r="F51" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B52" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>429</v>
+        <v>271</v>
       </c>
       <c r="F52" t="n">
         <v>16</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B53" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,18 +1598,18 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>270</v>
+        <v>114</v>
       </c>
       <c r="F53" t="n">
-        <v>16</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>194</v>
+        <v>335</v>
       </c>
       <c r="F54" t="n">
         <v>16</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B55" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="F55" t="n">
         <v>16</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B56" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>323</v>
+        <v>55</v>
       </c>
       <c r="F56" t="n">
         <v>16</v>
@@ -1675,7 +1675,7 @@
         <v>8</v>
       </c>
       <c r="B57" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>271</v>
+        <v>326</v>
       </c>
       <c r="F57" t="n">
         <v>16</v>
@@ -1697,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="B58" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>156</v>
+        <v>439</v>
       </c>
       <c r="F58" t="n">
         <v>16</v>
@@ -1719,7 +1719,7 @@
         <v>9</v>
       </c>
       <c r="B59" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1730,18 +1730,18 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>342</v>
+        <v>212</v>
       </c>
       <c r="F59" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B60" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1752,15 +1752,15 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>156</v>
+        <v>73</v>
       </c>
       <c r="F60" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B61" t="n">
         <v>14</v>
@@ -1774,18 +1774,18 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="F61" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="F62" t="n">
         <v>16</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B63" t="n">
         <v>15</v>
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>439</v>
+        <v>148</v>
       </c>
       <c r="F63" t="n">
         <v>16</v>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B64" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>335</v>
+        <v>97</v>
       </c>
       <c r="F64" t="n">
         <v>16</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B65" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1862,18 +1862,18 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>73</v>
+        <v>232</v>
       </c>
       <c r="F65" t="n">
-        <v>70</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B66" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1884,18 +1884,18 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="F66" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B67" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1906,18 +1906,18 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>240</v>
+        <v>172</v>
       </c>
       <c r="F67" t="n">
-        <v>16</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B68" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1928,18 +1928,18 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>59</v>
+        <v>247</v>
       </c>
       <c r="F68" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B69" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1950,18 +1950,18 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="F69" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B70" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F70" t="n">
         <v>10</v>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B71" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1994,18 +1994,18 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>416</v>
+        <v>104</v>
       </c>
       <c r="F71" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B72" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2016,18 +2016,18 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>139</v>
+        <v>214</v>
       </c>
       <c r="F72" t="n">
-        <v>16</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B73" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2038,18 +2038,18 @@
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="F73" t="n">
-        <v>164</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B74" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="F74" t="n">
         <v>16</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B75" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="F75" t="n">
         <v>16</v>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B76" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="F76" t="n">
         <v>16</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B77" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -2126,15 +2126,15 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>191</v>
+        <v>110</v>
       </c>
       <c r="F77" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B78" t="n">
         <v>29</v>
@@ -2148,18 +2148,18 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="F78" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B79" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2170,19 +2170,19 @@
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>415</v>
+        <v>175</v>
       </c>
       <c r="F79" t="n">
-        <v>21</v>
+        <v>130</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
+        <v>18</v>
+      </c>
+      <c r="B80" t="n">
         <v>24</v>
       </c>
-      <c r="B80" t="n">
-        <v>25</v>
-      </c>
       <c r="C80" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -2192,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>148</v>
+        <v>270</v>
       </c>
       <c r="F80" t="n">
         <v>16</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B81" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2214,18 +2214,18 @@
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F81" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B82" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2236,18 +2236,18 @@
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>277</v>
+        <v>32</v>
       </c>
       <c r="F82" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B83" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="F83" t="n">
         <v>16</v>
@@ -2266,10 +2266,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B84" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -2280,18 +2280,18 @@
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="F84" t="n">
-        <v>16</v>
+        <v>127</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B85" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="F85" t="n">
         <v>16</v>
@@ -2310,11 +2310,11 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
+        <v>21</v>
+      </c>
+      <c r="B86" t="n">
         <v>26</v>
       </c>
-      <c r="B86" t="n">
-        <v>29</v>
-      </c>
       <c r="C86" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -2324,7 +2324,7 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>198</v>
+        <v>30</v>
       </c>
       <c r="F86" t="n">
         <v>16</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B87" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2346,10 +2346,10 @@
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="F87" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88">
@@ -2357,7 +2357,7 @@
         <v>27</v>
       </c>
       <c r="B88" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2368,18 +2368,18 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="F88" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B89" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>175</v>
+        <v>416</v>
       </c>
       <c r="F89" t="n">
-        <v>130</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90">
@@ -2401,7 +2401,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2412,10 +2412,10 @@
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>383</v>
+        <v>89</v>
       </c>
       <c r="F90" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91">
@@ -2423,7 +2423,7 @@
         <v>29</v>
       </c>
       <c r="B91" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2434,15 +2434,15 @@
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>94</v>
+        <v>191</v>
       </c>
       <c r="F91" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B92" t="n">
         <v>32</v>
@@ -2456,15 +2456,15 @@
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>210</v>
+        <v>64</v>
       </c>
       <c r="F92" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B93" t="n">
         <v>33</v>
@@ -2478,18 +2478,18 @@
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>120</v>
+        <v>415</v>
       </c>
       <c r="F93" t="n">
-        <v>107</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B94" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2500,15 +2500,15 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="F94" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B95" t="n">
         <v>33</v>
@@ -2522,7 +2522,7 @@
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>86</v>
+        <v>383</v>
       </c>
       <c r="F95" t="n">
         <v>21</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B96" t="n">
         <v>34</v>
@@ -2544,18 +2544,18 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>243</v>
+        <v>120</v>
       </c>
       <c r="F96" t="n">
-        <v>21</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B97" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>226</v>
+        <v>34</v>
       </c>
       <c r="F97" t="n">
-        <v>157</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98">
@@ -2588,10 +2588,76 @@
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F98" t="n">
         <v>21</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>33</v>
+      </c>
+      <c r="B99" t="n">
+        <v>35</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>243</v>
+      </c>
+      <c r="F99" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>34</v>
+      </c>
+      <c r="B100" t="n">
+        <v>35</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>99</v>
+      </c>
+      <c r="F100" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>4</v>
+      </c>
+      <c r="B101" t="n">
+        <v>18</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>258</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/4697.xlsx
+++ b/output/topology_excel/4697.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,42 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
         </is>
       </c>
     </row>
@@ -481,6 +511,12 @@
       <c r="F2" t="n">
         <v>16</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +539,12 @@
       <c r="F3" t="n">
         <v>16</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +567,12 @@
       <c r="F4" t="n">
         <v>16</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +595,12 @@
       <c r="F5" t="n">
         <v>16</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +623,12 @@
       <c r="F6" t="n">
         <v>16</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +651,12 @@
       <c r="F7" t="n">
         <v>13</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +679,12 @@
       <c r="F8" t="n">
         <v>16</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +707,12 @@
       <c r="F9" t="n">
         <v>16</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +735,12 @@
       <c r="F10" t="n">
         <v>16</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +763,12 @@
       <c r="F11" t="n">
         <v>16</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +791,12 @@
       <c r="F12" t="n">
         <v>16</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +819,12 @@
       <c r="F13" t="n">
         <v>16</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +847,12 @@
       <c r="F14" t="n">
         <v>16</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +875,12 @@
       <c r="F15" t="n">
         <v>16</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +903,12 @@
       <c r="F16" t="n">
         <v>23</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +931,12 @@
       <c r="F17" t="n">
         <v>10</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +959,12 @@
       <c r="F18" t="n">
         <v>10</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +987,12 @@
       <c r="F19" t="n">
         <v>14</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +1015,12 @@
       <c r="F20" t="n">
         <v>16</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +1043,12 @@
       <c r="F21" t="n">
         <v>16</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +1071,12 @@
       <c r="F22" t="n">
         <v>16</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1099,12 @@
       <c r="F23" t="n">
         <v>18</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1127,12 @@
       <c r="F24" t="n">
         <v>16</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1155,12 @@
       <c r="F25" t="n">
         <v>17</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1183,12 @@
       <c r="F26" t="n">
         <v>16</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1211,12 @@
       <c r="F27" t="n">
         <v>16</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1239,12 @@
       <c r="F28" t="n">
         <v>16</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1267,12 @@
       <c r="F29" t="n">
         <v>16</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1295,12 @@
       <c r="F30" t="n">
         <v>16</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1323,12 @@
       <c r="F31" t="n">
         <v>21</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1351,12 @@
       <c r="F32" t="n">
         <v>21</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1379,12 @@
       <c r="F33" t="n">
         <v>21</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1407,12 @@
       <c r="F34" t="n">
         <v>16</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1435,12 @@
       <c r="F35" t="n">
         <v>16</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1463,12 @@
       <c r="F36" t="n">
         <v>16</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1491,12 @@
       <c r="F37" t="n">
         <v>16</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1265,14 +1511,24 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>342</v>
+        <v>34</v>
       </c>
       <c r="F38" t="n">
-        <v>50</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G38" t="n">
+        <v>326</v>
+      </c>
+      <c r="H38" t="n">
+        <v>16</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1293,8 +1549,14 @@
         <v>277</v>
       </c>
       <c r="F39" t="n">
-        <v>17</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1579,12 @@
       <c r="F40" t="n">
         <v>16</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1607,12 @@
       <c r="F41" t="n">
         <v>16</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1353,14 +1627,24 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>226</v>
+        <v>141</v>
       </c>
       <c r="F42" t="n">
-        <v>157</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G42" t="n">
+        <v>210</v>
+      </c>
+      <c r="H42" t="n">
+        <v>16</v>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1667,12 @@
       <c r="F43" t="n">
         <v>16</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1695,12 @@
       <c r="F44" t="n">
         <v>16</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1723,12 @@
       <c r="F45" t="n">
         <v>16</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1441,14 +1743,24 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="F46" t="n">
-        <v>56</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G46" t="n">
+        <v>40</v>
+      </c>
+      <c r="H46" t="n">
+        <v>16</v>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1783,12 @@
       <c r="F47" t="n">
         <v>18</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1811,12 @@
       <c r="F48" t="n">
         <v>16</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1839,12 @@
       <c r="F49" t="n">
         <v>16</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1867,12 @@
       <c r="F50" t="n">
         <v>16</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1895,12 @@
       <c r="F51" t="n">
         <v>16</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +1923,12 @@
       <c r="F52" t="n">
         <v>16</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1595,14 +1943,24 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="F53" t="n">
-        <v>94</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G53" t="n">
+        <v>78</v>
+      </c>
+      <c r="H53" t="n">
+        <v>16</v>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +1983,12 @@
       <c r="F54" t="n">
         <v>16</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +2011,12 @@
       <c r="F55" t="n">
         <v>16</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1669,6 +2039,12 @@
       <c r="F56" t="n">
         <v>16</v>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1691,6 +2067,12 @@
       <c r="F57" t="n">
         <v>16</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1713,6 +2095,12 @@
       <c r="F58" t="n">
         <v>16</v>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1735,6 +2123,12 @@
       <c r="F59" t="n">
         <v>16</v>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1749,14 +2143,24 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F60" t="n">
-        <v>70</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G60" t="n">
+        <v>59</v>
+      </c>
+      <c r="H60" t="n">
+        <v>14</v>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1779,6 +2183,12 @@
       <c r="F61" t="n">
         <v>14</v>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1801,6 +2211,12 @@
       <c r="F62" t="n">
         <v>16</v>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1823,6 +2239,12 @@
       <c r="F63" t="n">
         <v>16</v>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1845,6 +2267,12 @@
       <c r="F64" t="n">
         <v>16</v>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1859,13 +2287,31 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
-        <v>232</v>
+        <v>139</v>
       </c>
       <c r="F65" t="n">
-        <v>218</v>
+        <v>16</v>
+      </c>
+      <c r="G65" t="n">
+        <v>58</v>
+      </c>
+      <c r="H65" t="n">
+        <v>16</v>
+      </c>
+      <c r="I65" t="n">
+        <v>61</v>
+      </c>
+      <c r="J65" t="n">
+        <v>16</v>
+      </c>
+      <c r="K65" t="n">
+        <v>128</v>
+      </c>
+      <c r="L65" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="66">
@@ -1889,6 +2335,12 @@
       <c r="F66" t="n">
         <v>9</v>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1903,14 +2355,24 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="F67" t="n">
-        <v>87</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G67" t="n">
+        <v>71</v>
+      </c>
+      <c r="H67" t="n">
+        <v>16</v>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1933,6 +2395,12 @@
       <c r="F68" t="n">
         <v>23</v>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1955,6 +2423,12 @@
       <c r="F69" t="n">
         <v>16</v>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1977,6 +2451,12 @@
       <c r="F70" t="n">
         <v>10</v>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1999,6 +2479,12 @@
       <c r="F71" t="n">
         <v>10</v>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2013,14 +2499,24 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="F72" t="n">
-        <v>164</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G72" t="n">
+        <v>148</v>
+      </c>
+      <c r="H72" t="n">
+        <v>16</v>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2043,6 +2539,12 @@
       <c r="F73" t="n">
         <v>16</v>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2065,6 +2567,12 @@
       <c r="F74" t="n">
         <v>16</v>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2087,6 +2595,12 @@
       <c r="F75" t="n">
         <v>16</v>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2109,6 +2623,12 @@
       <c r="F76" t="n">
         <v>16</v>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2131,6 +2651,12 @@
       <c r="F77" t="n">
         <v>16</v>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2153,6 +2679,12 @@
       <c r="F78" t="n">
         <v>16</v>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2167,14 +2699,24 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="F79" t="n">
-        <v>130</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G79" t="n">
+        <v>114</v>
+      </c>
+      <c r="H79" t="n">
+        <v>16</v>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2197,6 +2739,12 @@
       <c r="F80" t="n">
         <v>16</v>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2219,6 +2767,12 @@
       <c r="F81" t="n">
         <v>14</v>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2241,6 +2795,12 @@
       <c r="F82" t="n">
         <v>14</v>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2263,6 +2823,12 @@
       <c r="F83" t="n">
         <v>16</v>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2277,14 +2843,28 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="F84" t="n">
-        <v>127</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G84" t="n">
+        <v>101</v>
+      </c>
+      <c r="H84" t="n">
+        <v>13</v>
+      </c>
+      <c r="I84" t="n">
+        <v>115</v>
+      </c>
+      <c r="J84" t="n">
+        <v>13</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2307,6 +2887,12 @@
       <c r="F85" t="n">
         <v>16</v>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2329,6 +2915,12 @@
       <c r="F86" t="n">
         <v>16</v>
       </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2351,6 +2943,12 @@
       <c r="F87" t="n">
         <v>13</v>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2373,6 +2971,12 @@
       <c r="F88" t="n">
         <v>10</v>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2395,6 +2999,12 @@
       <c r="F89" t="n">
         <v>18</v>
       </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2417,6 +3027,12 @@
       <c r="F90" t="n">
         <v>16</v>
       </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2431,14 +3047,24 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>191</v>
+        <v>153</v>
       </c>
       <c r="F91" t="n">
+        <v>16</v>
+      </c>
+      <c r="G91" t="n">
+        <v>24</v>
+      </c>
+      <c r="H91" t="n">
         <v>21</v>
       </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2461,6 +3087,12 @@
       <c r="F92" t="n">
         <v>21</v>
       </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2483,6 +3115,12 @@
       <c r="F93" t="n">
         <v>21</v>
       </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2505,6 +3143,12 @@
       <c r="F94" t="n">
         <v>16</v>
       </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2527,6 +3171,12 @@
       <c r="F95" t="n">
         <v>21</v>
       </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2541,14 +3191,24 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="F96" t="n">
-        <v>107</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G96" t="n">
+        <v>86</v>
+      </c>
+      <c r="H96" t="n">
+        <v>21</v>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2571,6 +3231,12 @@
       <c r="F97" t="n">
         <v>21</v>
       </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2593,6 +3259,12 @@
       <c r="F98" t="n">
         <v>21</v>
       </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2615,6 +3287,12 @@
       <c r="F99" t="n">
         <v>21</v>
       </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2637,6 +3315,12 @@
       <c r="F100" t="n">
         <v>21</v>
       </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2659,6 +3343,12 @@
       <c r="F101" t="n">
         <v>1</v>
       </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
